--- a/data/kindergarten/data(1).xlsx
+++ b/data/kindergarten/data(1).xlsx
@@ -800,7 +800,7 @@
         <v>134.137129</v>
       </c>
       <c r="D16" t="str">
-        <v>高松市立田井幼稚園（令和2年4月1日から休園）</v>
+        <v>高松市立田井こども園</v>
       </c>
       <c r="E16" t="str">
         <v>高松市牟礼町牟礼1243-2</v>
@@ -826,7 +826,7 @@
         <v>134.148384</v>
       </c>
       <c r="D17" t="str">
-        <v>高松市立大町幼稚園</v>
+        <v>高松市立旧大町幼稚園</v>
       </c>
       <c r="E17" t="str">
         <v>高松市牟礼町牟礼100-1</v>
@@ -1372,7 +1372,7 @@
         <v>134.052507</v>
       </c>
       <c r="D38" t="str">
-        <v>光華幼稚園</v>
+        <v>認定こども園光華幼稚園</v>
       </c>
       <c r="E38" t="str">
         <v>高松市瓦町一丁目13-8</v>
@@ -1424,7 +1424,7 @@
         <v>134.095292</v>
       </c>
       <c r="D40" t="str">
-        <v>屋島教会幼稚園</v>
+        <v>幼稚園型認定こども園屋島教会幼稚園</v>
       </c>
       <c r="E40" t="str">
         <v>高松市屋島西町1392-7</v>
